--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_70/per_file_predictions_epoch_70.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_70/per_file_predictions_epoch_70.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.2238,0.4670,0.0051,0.2140</t>
-  </si>
-  <si>
-    <t>0.0097,0.0036,0.0004,0.9955</t>
-  </si>
-  <si>
-    <t>0.8368,0.0273,0.0167,0.0777</t>
-  </si>
-  <si>
-    <t>0.2230,0.0194,0.0143,0.8716</t>
-  </si>
-  <si>
-    <t>0.9917,0.0064,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9958,0.0020,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9537,0.0325,0.0078,0.0028</t>
-  </si>
-  <si>
-    <t>0.9833,0.0072,0.0010,0.0025</t>
-  </si>
-  <si>
-    <t>0.9906,0.0112,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9922,0.0032,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9968,0.0002,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9950,0.0018,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.6289,0.0927,0.3454,0.0158</t>
-  </si>
-  <si>
-    <t>0.2463,0.0241,0.7832,0.0003</t>
-  </si>
-  <si>
-    <t>0.2170,0.0236,0.7915,0.0001</t>
-  </si>
-  <si>
-    <t>0.1027,0.0122,0.9236,0.0005</t>
-  </si>
-  <si>
-    <t>0.7693,0.2080,0.0210,0.0089</t>
-  </si>
-  <si>
-    <t>0.0086,0.9832,0.0039,0.0025</t>
-  </si>
-  <si>
-    <t>0.0611,0.9549,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.2742,0.8146,0.0060,0.0027</t>
-  </si>
-  <si>
-    <t>0.0610,0.9558,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0024,0.9946,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.5860,0.0204,0.4772,0.0122</t>
-  </si>
-  <si>
-    <t>0.2155,0.0244,0.7758,0.0084</t>
-  </si>
-  <si>
-    <t>0.0074,0.0075,0.9710,0.0084</t>
-  </si>
-  <si>
-    <t>0.5573,0.0901,0.3417,0.0550</t>
-  </si>
-  <si>
-    <t>0.4908,0.0091,0.6621,0.0068</t>
-  </si>
-  <si>
-    <t>0.0526,0.0231,0.9041,0.0162</t>
-  </si>
-  <si>
-    <t>0.0105,0.0041,0.9880,0.0011</t>
-  </si>
-  <si>
-    <t>0.0930,0.9348,0.0023,0.0014</t>
-  </si>
-  <si>
-    <t>0.0885,0.4728,0.5698,0.0014</t>
-  </si>
-  <si>
-    <t>0.0189,0.0073,0.9783,0.0009</t>
-  </si>
-  <si>
-    <t>0.0097,0.9423,0.0731,0.0040</t>
-  </si>
-  <si>
-    <t>0.8486,0.1080,0.0109,0.0205</t>
-  </si>
-  <si>
-    <t>0.2708,0.1837,0.4829,0.0014</t>
-  </si>
-  <si>
-    <t>0.7486,0.3823,0.0083,0.0016</t>
-  </si>
-  <si>
-    <t>0.0007,0.9933,0.1718,0.0016</t>
-  </si>
-  <si>
-    <t>0.0040,0.9771,0.0083,0.0029</t>
-  </si>
-  <si>
-    <t>0.1527,0.0618,0.8337,0.0170</t>
-  </si>
-  <si>
-    <t>0.1400,0.0956,0.5496,0.2888</t>
-  </si>
-  <si>
-    <t>0.0624,0.0670,0.8013,0.1100</t>
-  </si>
-  <si>
-    <t>0.0419,0.0500,0.9452,0.0022</t>
-  </si>
-  <si>
-    <t>0.0049,0.9803,0.0067,0.0000</t>
-  </si>
-  <si>
-    <t>0.1201,0.1459,0.7870,0.0233</t>
-  </si>
-  <si>
-    <t>0.0086,0.9279,0.0087,0.3433</t>
-  </si>
-  <si>
-    <t>0.0015,0.9928,0.0144,0.0013</t>
-  </si>
-  <si>
-    <t>0.0048,0.9748,0.1061,0.0018</t>
-  </si>
-  <si>
-    <t>0.0003,0.9972,0.0099,0.0011</t>
-  </si>
-  <si>
-    <t>0.0063,0.1846,0.9769,0.0019</t>
-  </si>
-  <si>
-    <t>0.0038,0.2601,0.9799,0.0010</t>
-  </si>
-  <si>
-    <t>0.0670,0.0230,0.9126,0.0149</t>
-  </si>
-  <si>
-    <t>0.0591,0.0084,0.9559,0.0016</t>
-  </si>
-  <si>
-    <t>0.0182,0.0111,0.9731,0.0048</t>
-  </si>
-  <si>
-    <t>0.0235,0.0218,0.9644,0.0004</t>
-  </si>
-  <si>
-    <t>0.8322,0.2312,0.0123,0.0014</t>
-  </si>
-  <si>
-    <t>0.9760,0.0093,0.0031,0.0043</t>
-  </si>
-  <si>
-    <t>0.9839,0.0087,0.0005,0.0011</t>
-  </si>
-  <si>
-    <t>0.0030,0.0496,0.9826,0.0085</t>
-  </si>
-  <si>
-    <t>0.9834,0.0048,0.0006,0.0028</t>
-  </si>
-  <si>
-    <t>0.9748,0.0182,0.0011,0.0017</t>
-  </si>
-  <si>
-    <t>0.9502,0.0469,0.0040,0.0018</t>
-  </si>
-  <si>
-    <t>0.0043,0.8612,0.8737,0.0012</t>
-  </si>
-  <si>
-    <t>0.0125,0.1636,0.9249,0.0233</t>
-  </si>
-  <si>
-    <t>0.0122,0.2288,0.9411,0.0059</t>
-  </si>
-  <si>
-    <t>0.0007,0.9279,0.9433,0.0002</t>
-  </si>
-  <si>
-    <t>0.0060,0.0254,0.9908,0.0002</t>
-  </si>
-  <si>
-    <t>0.0173,0.9593,0.0109,0.0004</t>
-  </si>
-  <si>
-    <t>0.0166,0.9771,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.9161,0.0315,0.0483,0.0030</t>
-  </si>
-  <si>
-    <t>0.8386,0.0959,0.0334,0.0072</t>
-  </si>
-  <si>
-    <t>0.0265,0.5981,0.3814,0.0023</t>
-  </si>
-  <si>
-    <t>0.0006,0.8891,0.9320,0.0002</t>
-  </si>
-  <si>
-    <t>0.0047,0.8935,0.4102,0.0007</t>
-  </si>
-  <si>
-    <t>0.0121,0.8863,0.4666,0.0016</t>
-  </si>
-  <si>
-    <t>0.0030,0.9538,0.3070,0.0003</t>
-  </si>
-  <si>
-    <t>0.1935,0.0069,0.0266,0.8392</t>
-  </si>
-  <si>
-    <t>0.0015,0.1021,0.0014,0.9953</t>
-  </si>
-  <si>
-    <t>0.0023,0.0018,0.0004,0.9983</t>
-  </si>
-  <si>
-    <t>0.0107,0.0056,0.0084,0.9896</t>
-  </si>
-  <si>
-    <t>0.0752,0.0128,0.0542,0.9228</t>
-  </si>
-  <si>
-    <t>0.0092,0.0010,0.0003,0.9961</t>
-  </si>
-  <si>
-    <t>0.0030,0.9096,0.8740,0.0005</t>
-  </si>
-  <si>
-    <t>0.0063,0.5755,0.9570,0.0010</t>
-  </si>
-  <si>
-    <t>0.0287,0.4794,0.6735,0.0030</t>
-  </si>
-  <si>
-    <t>0.0028,0.3688,0.9449,0.0005</t>
-  </si>
-  <si>
-    <t>0.0019,0.9306,0.3580,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.9006,0.8096,0.0001</t>
-  </si>
-  <si>
-    <t>0.9932,0.0042,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9604,0.0546,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9597,0.0574,0.0038,0.0007</t>
-  </si>
-  <si>
-    <t>0.9928,0.0015,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9681,0.0376,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9757,0.0522,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9505,0.0482,0.0044,0.0017</t>
-  </si>
-  <si>
-    <t>0.9702,0.0429,0.0027,0.0003</t>
-  </si>
-  <si>
-    <t>0.9939,0.0043,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9932,0.0035,0.0010,0.0003</t>
-  </si>
-  <si>
-    <t>0.9908,0.0089,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9940,0.0013,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9898,0.0054,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.9764,0.0242,0.0045,0.0010</t>
-  </si>
-  <si>
-    <t>0.9966,0.0010,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9834,0.0173,0.0021,0.0005</t>
-  </si>
-  <si>
-    <t>0.0090,0.0062,0.9794,0.0065</t>
-  </si>
-  <si>
-    <t>0.0890,0.0152,0.9101,0.0026</t>
-  </si>
-  <si>
-    <t>0.4083,0.0360,0.2945,0.2662</t>
-  </si>
-  <si>
-    <t>0.0608,0.0287,0.9150,0.0008</t>
-  </si>
-  <si>
-    <t>0.0357,0.9620,0.0014,0.0009</t>
-  </si>
-  <si>
-    <t>0.0453,0.9559,0.0024,0.0017</t>
-  </si>
-  <si>
-    <t>0.0107,0.9841,0.0005,0.0015</t>
-  </si>
-  <si>
-    <t>0.4398,0.7203,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.2185,0.8298,0.0028,0.0042</t>
-  </si>
-  <si>
-    <t>0.0404,0.9567,0.0027,0.0002</t>
-  </si>
-  <si>
-    <t>0.7875,0.3705,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.6847,0.1219,0.1777,0.0310</t>
-  </si>
-  <si>
-    <t>0.1560,0.0655,0.7689,0.0232</t>
-  </si>
-  <si>
-    <t>0.5411,0.2246,0.3105,0.0153</t>
-  </si>
-  <si>
-    <t>0.5030,0.1602,0.3888,0.0473</t>
-  </si>
-  <si>
-    <t>0.1230,0.5562,0.0395,0.5967</t>
-  </si>
-  <si>
-    <t>0.0007,0.9954,0.0068,0.0011</t>
-  </si>
-  <si>
-    <t>0.0007,0.9951,0.0098,0.0008</t>
-  </si>
-  <si>
-    <t>0.0075,0.9774,0.0078,0.0023</t>
-  </si>
-  <si>
-    <t>0.0001,0.9747,0.9072,0.0001</t>
-  </si>
-  <si>
-    <t>0.0086,0.9873,0.0081,0.0002</t>
-  </si>
-  <si>
-    <t>0.5792,0.5115,0.0119,0.0040</t>
-  </si>
-  <si>
-    <t>0.7607,0.3900,0.0054,0.0008</t>
-  </si>
-  <si>
-    <t>0.9780,0.0224,0.0068,0.0003</t>
-  </si>
-  <si>
-    <t>0.9861,0.0064,0.0030,0.0007</t>
-  </si>
-  <si>
-    <t>0.9815,0.0057,0.0008,0.0028</t>
-  </si>
-  <si>
-    <t>0.9741,0.0235,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9803,0.0048,0.0020,0.0034</t>
-  </si>
-  <si>
-    <t>0.9561,0.0492,0.0091,0.0015</t>
-  </si>
-  <si>
-    <t>0.9573,0.0155,0.0073,0.0077</t>
-  </si>
-  <si>
-    <t>0.9710,0.0224,0.0027,0.0018</t>
-  </si>
-  <si>
-    <t>0.0035,0.8675,0.7846,0.0011</t>
-  </si>
-  <si>
-    <t>0.0160,0.4453,0.8983,0.0061</t>
-  </si>
-  <si>
-    <t>0.0066,0.1768,0.9483,0.0022</t>
-  </si>
-  <si>
-    <t>0.0131,0.2613,0.8817,0.0005</t>
-  </si>
-  <si>
-    <t>0.5740,0.3232,0.1104,0.0274</t>
-  </si>
-  <si>
-    <t>0.1146,0.6600,0.1909,0.0552</t>
-  </si>
-  <si>
-    <t>0.6594,0.0040,0.5336,0.0084</t>
-  </si>
-  <si>
-    <t>0.1550,0.7599,0.0450,0.0294</t>
-  </si>
-  <si>
-    <t>0.0682,0.0028,0.0023,0.9743</t>
-  </si>
-  <si>
-    <t>0.0005,0.0016,0.0009,0.9992</t>
-  </si>
-  <si>
-    <t>0.0046,0.0072,0.0023,0.9958</t>
-  </si>
-  <si>
-    <t>0.0502,0.0069,0.0095,0.9700</t>
-  </si>
-  <si>
-    <t>0.0042,0.9268,0.4044,0.0005</t>
-  </si>
-  <si>
-    <t>0.9614,0.0170,0.0073,0.0062</t>
-  </si>
-  <si>
-    <t>0.5587,0.4646,0.0415,0.0114</t>
-  </si>
-  <si>
-    <t>0.9290,0.0782,0.0020,0.0030</t>
-  </si>
-  <si>
-    <t>0.8150,0.3020,0.0070,0.0007</t>
-  </si>
-  <si>
-    <t>0.9189,0.0132,0.0134,0.0237</t>
-  </si>
-  <si>
-    <t>0.3323,0.0023,0.0112,0.7888</t>
-  </si>
-  <si>
-    <t>0.9673,0.0076,0.0028,0.0088</t>
-  </si>
-  <si>
-    <t>0.0007,0.2471,0.9726,0.0162</t>
-  </si>
-  <si>
-    <t>0.8716,0.0167,0.0149,0.0501</t>
-  </si>
-  <si>
-    <t>0.8794,0.0143,0.0072,0.0715</t>
-  </si>
-  <si>
-    <t>0.3860,0.7341,0.0018,0.0015</t>
-  </si>
-  <si>
-    <t>0.9113,0.0553,0.0043,0.0053</t>
-  </si>
-  <si>
-    <t>0.9436,0.0654,0.0065,0.0006</t>
-  </si>
-  <si>
-    <t>0.4229,0.4391,0.1329,0.0094</t>
-  </si>
-  <si>
-    <t>0.9158,0.0293,0.0286,0.0040</t>
-  </si>
-  <si>
-    <t>0.8544,0.1671,0.0050,0.0049</t>
-  </si>
-  <si>
-    <t>0.9848,0.0058,0.0011,0.0022</t>
-  </si>
-  <si>
-    <t>0.9691,0.0202,0.0023,0.0032</t>
-  </si>
-  <si>
-    <t>0.9904,0.0012,0.0008,0.0022</t>
-  </si>
-  <si>
-    <t>0.9686,0.0091,0.0015,0.0053</t>
-  </si>
-  <si>
-    <t>0.9696,0.0235,0.0006,0.0015</t>
-  </si>
-  <si>
-    <t>0.9615,0.0440,0.0048,0.0009</t>
-  </si>
-  <si>
-    <t>0.9891,0.0045,0.0013,0.0010</t>
-  </si>
-  <si>
-    <t>0.9879,0.0060,0.0013,0.0008</t>
-  </si>
-  <si>
-    <t>0.4481,0.6629,0.0071,0.0078</t>
-  </si>
-  <si>
-    <t>0.8070,0.2764,0.0056,0.0012</t>
-  </si>
-  <si>
-    <t>0.8288,0.2466,0.0069,0.0026</t>
-  </si>
-  <si>
-    <t>0.5616,0.1701,0.4024,0.0084</t>
-  </si>
-  <si>
-    <t>0.9180,0.1610,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.8642,0.1453,0.0115,0.0046</t>
-  </si>
-  <si>
-    <t>0.9605,0.0643,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.9202,0.0883,0.0116,0.0035</t>
-  </si>
-  <si>
-    <t>0.0064,0.0524,0.9879,0.0007</t>
-  </si>
-  <si>
-    <t>0.8954,0.0953,0.0217,0.0007</t>
-  </si>
-  <si>
-    <t>0.0045,0.0331,0.9741,0.0033</t>
-  </si>
-  <si>
-    <t>0.0056,0.1066,0.9728,0.0045</t>
-  </si>
-  <si>
-    <t>0.0669,0.0202,0.9228,0.0010</t>
-  </si>
-  <si>
-    <t>0.0217,0.0337,0.9675,0.0047</t>
-  </si>
-  <si>
-    <t>0.0452,0.0582,0.9229,0.0014</t>
-  </si>
-  <si>
-    <t>0.0543,0.0260,0.9354,0.0025</t>
-  </si>
-  <si>
-    <t>0.0113,0.0016,0.9901,0.0006</t>
-  </si>
-  <si>
-    <t>0.1855,0.1028,0.7653,0.0100</t>
-  </si>
-  <si>
-    <t>0.1394,0.2768,0.6049,0.0139</t>
-  </si>
-  <si>
-    <t>0.6952,0.1193,0.2001,0.0112</t>
-  </si>
-  <si>
-    <t>0.3099,0.1055,0.5800,0.0083</t>
-  </si>
-  <si>
-    <t>0.1371,0.0475,0.8254,0.0018</t>
-  </si>
-  <si>
-    <t>0.5567,0.3261,0.1569,0.0286</t>
-  </si>
-  <si>
-    <t>0.4564,0.1460,0.4380,0.0117</t>
-  </si>
-  <si>
-    <t>0.4540,0.0519,0.5435,0.0029</t>
-  </si>
-  <si>
-    <t>0.7298,0.4363,0.0048,0.0005</t>
-  </si>
-  <si>
-    <t>0.3892,0.7493,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.8615,0.2261,0.0045,0.0006</t>
-  </si>
-  <si>
-    <t>0.9280,0.1389,0.0023,0.0002</t>
-  </si>
-  <si>
-    <t>0.7767,0.4011,0.0025,0.0003</t>
-  </si>
-  <si>
-    <t>0.6313,0.0165,0.4752,0.0034</t>
-  </si>
-  <si>
-    <t>0.8934,0.0041,0.0602,0.0093</t>
-  </si>
-  <si>
-    <t>0.7800,0.0120,0.1449,0.0264</t>
-  </si>
-  <si>
-    <t>0.5333,0.0111,0.6014,0.0063</t>
-  </si>
-  <si>
-    <t>0.8219,0.0392,0.0726,0.0191</t>
-  </si>
-  <si>
-    <t>0.1173,0.0389,0.8514,0.0195</t>
-  </si>
-  <si>
-    <t>0.0083,0.1883,0.9326,0.0055</t>
-  </si>
-  <si>
-    <t>0.0131,0.3157,0.9533,0.0035</t>
-  </si>
-  <si>
-    <t>0.1341,0.0431,0.8677,0.0149</t>
-  </si>
-  <si>
-    <t>0.0289,0.4159,0.6874,0.0049</t>
-  </si>
-  <si>
-    <t>0.9759,0.0105,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9318,0.1384,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9730,0.0067,0.0007,0.0049</t>
-  </si>
-  <si>
-    <t>0.9855,0.0198,0.0014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9805,0.0238,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.9750,0.0286,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.9855,0.0052,0.0005,0.0020</t>
-  </si>
-  <si>
-    <t>0.9656,0.0249,0.0066,0.0022</t>
-  </si>
-  <si>
-    <t>0.1453,0.0168,0.8854,0.0050</t>
-  </si>
-  <si>
-    <t>0.1691,0.6419,0.2118,0.0046</t>
-  </si>
-  <si>
-    <t>0.9239,0.0365,0.0212,0.0061</t>
-  </si>
-  <si>
-    <t>0.0587,0.0363,0.9444,0.0035</t>
-  </si>
-  <si>
-    <t>0.0011,0.0130,0.9939,0.0015</t>
-  </si>
-  <si>
-    <t>0.0148,0.0688,0.9638,0.0035</t>
-  </si>
-  <si>
-    <t>0.0024,0.0182,0.9944,0.0002</t>
-  </si>
-  <si>
-    <t>0.1668,0.0587,0.7205,0.0092</t>
-  </si>
-  <si>
-    <t>0.0037,0.0118,0.9946,0.0003</t>
-  </si>
-  <si>
-    <t>0.0453,0.0152,0.9700,0.0006</t>
-  </si>
-  <si>
-    <t>0.0737,0.3769,0.5947,0.0024</t>
-  </si>
-  <si>
-    <t>0.7378,0.0038,0.5059,0.0008</t>
-  </si>
-  <si>
-    <t>0.8250,0.0029,0.2442,0.0037</t>
-  </si>
-  <si>
-    <t>0.6158,0.0341,0.4550,0.0100</t>
-  </si>
-  <si>
-    <t>0.9807,0.0264,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9872,0.0066,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.9880,0.0146,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9415,0.1366,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9598,0.0375,0.0023,0.0026</t>
-  </si>
-  <si>
-    <t>0.9893,0.0115,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9944,0.0060,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9843,0.0089,0.0012,0.0011</t>
-  </si>
-  <si>
-    <t>0.0995,0.0684,0.8696,0.0013</t>
-  </si>
-  <si>
-    <t>0.0014,0.0968,0.9886,0.0009</t>
-  </si>
-  <si>
-    <t>0.0221,0.2942,0.8466,0.0048</t>
-  </si>
-  <si>
-    <t>0.0531,0.0062,0.9500,0.0005</t>
-  </si>
-  <si>
-    <t>0.0154,0.0243,0.9684,0.0066</t>
-  </si>
-  <si>
-    <t>0.3996,0.0057,0.4201,0.1330</t>
-  </si>
-  <si>
-    <t>0.1710,0.0111,0.8709,0.0048</t>
-  </si>
-  <si>
-    <t>0.0501,0.1401,0.8231,0.0534</t>
-  </si>
-  <si>
-    <t>0.7948,0.0057,0.0031,0.2340</t>
-  </si>
-  <si>
-    <t>0.0086,0.0149,0.0029,0.9920</t>
-  </si>
-  <si>
-    <t>0.0703,0.0043,0.0062,0.9657</t>
-  </si>
-  <si>
-    <t>0.0045,0.0005,0.0012,0.9967</t>
-  </si>
-  <si>
-    <t>0.0096,0.0013,0.0007,0.9955</t>
-  </si>
-  <si>
-    <t>0.3330,0.1601,0.0565,0.5654</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.4854,0.2904,0.0178,0.1023</t>
+  </si>
+  <si>
+    <t>0.0133,0.0072,0.0036,0.9899</t>
+  </si>
+  <si>
+    <t>0.7431,0.0581,0.0004,0.0459</t>
+  </si>
+  <si>
+    <t>0.0289,0.0085,0.0009,0.9869</t>
+  </si>
+  <si>
+    <t>0.9922,0.0023,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9916,0.0057,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9790,0.0215,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.9924,0.0017,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9870,0.0100,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9899,0.0125,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9869,0.0147,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9936,0.0009,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.5216,0.2087,0.3480,0.0138</t>
+  </si>
+  <si>
+    <t>0.3656,0.1167,0.5534,0.0154</t>
+  </si>
+  <si>
+    <t>0.2529,0.0071,0.8703,0.0009</t>
+  </si>
+  <si>
+    <t>0.2160,0.3490,0.2868,0.0050</t>
+  </si>
+  <si>
+    <t>0.8007,0.0672,0.1152,0.0035</t>
+  </si>
+  <si>
+    <t>0.0136,0.9805,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.0118,0.9873,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.2604,0.8277,0.0054,0.0010</t>
+  </si>
+  <si>
+    <t>0.5048,0.6905,0.0058,0.0025</t>
+  </si>
+  <si>
+    <t>0.0215,0.9779,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.6546,0.0088,0.1962,0.1029</t>
+  </si>
+  <si>
+    <t>0.4907,0.0587,0.5452,0.0067</t>
+  </si>
+  <si>
+    <t>0.0207,0.0355,0.9576,0.0081</t>
+  </si>
+  <si>
+    <t>0.0249,0.0110,0.9400,0.0222</t>
+  </si>
+  <si>
+    <t>0.2674,0.0202,0.7941,0.0041</t>
+  </si>
+  <si>
+    <t>0.0669,0.0078,0.9444,0.0024</t>
+  </si>
+  <si>
+    <t>0.0004,0.0017,0.9858,0.0316</t>
+  </si>
+  <si>
+    <t>0.8349,0.3181,0.0042,0.0005</t>
+  </si>
+  <si>
+    <t>0.2630,0.1289,0.6424,0.0031</t>
+  </si>
+  <si>
+    <t>0.0130,0.0218,0.9838,0.0004</t>
+  </si>
+  <si>
+    <t>0.0219,0.7599,0.5380,0.0025</t>
+  </si>
+  <si>
+    <t>0.8418,0.1164,0.0348,0.0074</t>
+  </si>
+  <si>
+    <t>0.7185,0.3954,0.0106,0.0006</t>
+  </si>
+  <si>
+    <t>0.6220,0.5908,0.0030,0.0018</t>
+  </si>
+  <si>
+    <t>0.0051,0.9813,0.1032,0.0005</t>
+  </si>
+  <si>
+    <t>0.0088,0.8846,0.1769,0.0345</t>
+  </si>
+  <si>
+    <t>0.0685,0.3615,0.8250,0.0349</t>
+  </si>
+  <si>
+    <t>0.0527,0.0763,0.8680,0.0700</t>
+  </si>
+  <si>
+    <t>0.2743,0.0128,0.6543,0.0728</t>
+  </si>
+  <si>
+    <t>0.0175,0.1612,0.9359,0.0040</t>
+  </si>
+  <si>
+    <t>0.0093,0.9453,0.0444,0.0008</t>
+  </si>
+  <si>
+    <t>0.0314,0.0234,0.9638,0.0018</t>
+  </si>
+  <si>
+    <t>0.0269,0.7953,0.0151,0.6279</t>
+  </si>
+  <si>
+    <t>0.0005,0.9950,0.0046,0.0038</t>
+  </si>
+  <si>
+    <t>0.0017,0.9726,0.1872,0.0016</t>
+  </si>
+  <si>
+    <t>0.0008,0.9943,0.0182,0.0011</t>
+  </si>
+  <si>
+    <t>0.0092,0.1060,0.9690,0.0023</t>
+  </si>
+  <si>
+    <t>0.0040,0.5033,0.9625,0.0005</t>
+  </si>
+  <si>
+    <t>0.0845,0.0426,0.8858,0.0030</t>
+  </si>
+  <si>
+    <t>0.0810,0.0070,0.8256,0.0891</t>
+  </si>
+  <si>
+    <t>0.0143,0.0173,0.9726,0.0043</t>
+  </si>
+  <si>
+    <t>0.0392,0.0116,0.9586,0.0024</t>
+  </si>
+  <si>
+    <t>0.7956,0.3031,0.0063,0.0021</t>
+  </si>
+  <si>
+    <t>0.9724,0.0304,0.0045,0.0008</t>
+  </si>
+  <si>
+    <t>0.9604,0.0386,0.0042,0.0028</t>
+  </si>
+  <si>
+    <t>0.0027,0.0144,0.9889,0.0048</t>
+  </si>
+  <si>
+    <t>0.9673,0.0261,0.0015,0.0022</t>
+  </si>
+  <si>
+    <t>0.9868,0.0108,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9595,0.0460,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.0046,0.8955,0.8509,0.0007</t>
+  </si>
+  <si>
+    <t>0.0029,0.0199,0.9655,0.0229</t>
+  </si>
+  <si>
+    <t>0.0058,0.0092,0.9899,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.9610,0.9698,0.0000</t>
+  </si>
+  <si>
+    <t>0.0065,0.0056,0.9892,0.0014</t>
+  </si>
+  <si>
+    <t>0.0502,0.7076,0.4164,0.0022</t>
+  </si>
+  <si>
+    <t>0.0054,0.9882,0.0026,0.0000</t>
+  </si>
+  <si>
+    <t>0.9189,0.0267,0.0340,0.0042</t>
+  </si>
+  <si>
+    <t>0.7023,0.1966,0.0385,0.0508</t>
+  </si>
+  <si>
+    <t>0.0026,0.0265,0.9879,0.0026</t>
+  </si>
+  <si>
+    <t>0.0019,0.9259,0.7310,0.0004</t>
+  </si>
+  <si>
+    <t>0.0014,0.9659,0.1452,0.0001</t>
+  </si>
+  <si>
+    <t>0.0027,0.9607,0.5076,0.0008</t>
+  </si>
+  <si>
+    <t>0.0013,0.8313,0.7588,0.0002</t>
+  </si>
+  <si>
+    <t>0.0237,0.0015,0.0133,0.9785</t>
+  </si>
+  <si>
+    <t>0.0024,0.0313,0.0009,0.9966</t>
+  </si>
+  <si>
+    <t>0.0017,0.0269,0.0006,0.9971</t>
+  </si>
+  <si>
+    <t>0.0071,0.0449,0.0042,0.9904</t>
+  </si>
+  <si>
+    <t>0.0070,0.1038,0.0085,0.9864</t>
+  </si>
+  <si>
+    <t>0.0123,0.0011,0.0030,0.9919</t>
+  </si>
+  <si>
+    <t>0.0013,0.9502,0.9149,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.8000,0.9399,0.0011</t>
+  </si>
+  <si>
+    <t>0.0136,0.0530,0.9714,0.0013</t>
+  </si>
+  <si>
+    <t>0.0050,0.7267,0.7806,0.0013</t>
+  </si>
+  <si>
+    <t>0.0004,0.9573,0.7166,0.0000</t>
+  </si>
+  <si>
+    <t>0.0030,0.7627,0.9071,0.0006</t>
+  </si>
+  <si>
+    <t>0.9780,0.0221,0.0056,0.0004</t>
+  </si>
+  <si>
+    <t>0.9829,0.0284,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.8595,0.1774,0.0118,0.0007</t>
+  </si>
+  <si>
+    <t>0.9899,0.0052,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9708,0.0315,0.0069,0.0007</t>
+  </si>
+  <si>
+    <t>0.9750,0.0225,0.0048,0.0014</t>
+  </si>
+  <si>
+    <t>0.9849,0.0125,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9720,0.0459,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9911,0.0025,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9964,0.0005,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9906,0.0032,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9973,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9955,0.0009,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9852,0.0121,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9927,0.0049,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9747,0.0339,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.0030,0.0064,0.9826,0.0119</t>
+  </si>
+  <si>
+    <t>0.0804,0.0413,0.9019,0.0043</t>
+  </si>
+  <si>
+    <t>0.5506,0.0659,0.4077,0.0501</t>
+  </si>
+  <si>
+    <t>0.0510,0.0079,0.9391,0.0075</t>
+  </si>
+  <si>
+    <t>0.0724,0.9432,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0105,0.9824,0.0067,0.0008</t>
+  </si>
+  <si>
+    <t>0.0085,0.9840,0.0015,0.0018</t>
+  </si>
+  <si>
+    <t>0.1591,0.8909,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.0859,0.9140,0.0140,0.0048</t>
+  </si>
+  <si>
+    <t>0.0269,0.9698,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.4675,0.6665,0.0044,0.0014</t>
+  </si>
+  <si>
+    <t>0.7627,0.0679,0.1198,0.0227</t>
+  </si>
+  <si>
+    <t>0.2903,0.0234,0.7517,0.0031</t>
+  </si>
+  <si>
+    <t>0.5278,0.3087,0.1757,0.0319</t>
+  </si>
+  <si>
+    <t>0.2884,0.4510,0.2057,0.0062</t>
+  </si>
+  <si>
+    <t>0.3320,0.3786,0.3111,0.2486</t>
+  </si>
+  <si>
+    <t>0.0009,0.9953,0.0105,0.0008</t>
+  </si>
+  <si>
+    <t>0.0072,0.9761,0.0316,0.0061</t>
+  </si>
+  <si>
+    <t>0.0008,0.9920,0.0046,0.0176</t>
+  </si>
+  <si>
+    <t>0.0006,0.9138,0.9108,0.0010</t>
+  </si>
+  <si>
+    <t>0.0130,0.9842,0.0051,0.0001</t>
+  </si>
+  <si>
+    <t>0.6849,0.4397,0.0127,0.0045</t>
+  </si>
+  <si>
+    <t>0.6894,0.4779,0.0120,0.0030</t>
+  </si>
+  <si>
+    <t>0.9758,0.0271,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.9746,0.0346,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9786,0.0079,0.0034,0.0024</t>
+  </si>
+  <si>
+    <t>0.9554,0.0580,0.0060,0.0003</t>
+  </si>
+  <si>
+    <t>0.9912,0.0025,0.0037,0.0005</t>
+  </si>
+  <si>
+    <t>0.9533,0.0414,0.0164,0.0013</t>
+  </si>
+  <si>
+    <t>0.9555,0.0317,0.0192,0.0011</t>
+  </si>
+  <si>
+    <t>0.9619,0.0218,0.0067,0.0031</t>
+  </si>
+  <si>
+    <t>0.0010,0.8909,0.9173,0.0005</t>
+  </si>
+  <si>
+    <t>0.0016,0.6586,0.9231,0.0001</t>
+  </si>
+  <si>
+    <t>0.0081,0.7522,0.4207,0.0011</t>
+  </si>
+  <si>
+    <t>0.0212,0.4001,0.8426,0.0055</t>
+  </si>
+  <si>
+    <t>0.8844,0.0933,0.0048,0.0042</t>
+  </si>
+  <si>
+    <t>0.5184,0.3231,0.1519,0.0183</t>
+  </si>
+  <si>
+    <t>0.5822,0.0082,0.6187,0.0020</t>
+  </si>
+  <si>
+    <t>0.7128,0.0558,0.2523,0.0018</t>
+  </si>
+  <si>
+    <t>0.3284,0.0016,0.0059,0.8044</t>
+  </si>
+  <si>
+    <t>0.0003,0.0047,0.0007,0.9993</t>
+  </si>
+  <si>
+    <t>0.0010,0.2377,0.0005,0.9925</t>
+  </si>
+  <si>
+    <t>0.0212,0.0025,0.0038,0.9876</t>
+  </si>
+  <si>
+    <t>0.0020,0.8369,0.8881,0.0006</t>
+  </si>
+  <si>
+    <t>0.9777,0.0086,0.0007,0.0031</t>
+  </si>
+  <si>
+    <t>0.2741,0.7551,0.0089,0.0096</t>
+  </si>
+  <si>
+    <t>0.9090,0.1015,0.0026,0.0044</t>
+  </si>
+  <si>
+    <t>0.9217,0.0911,0.0041,0.0015</t>
+  </si>
+  <si>
+    <t>0.9663,0.0085,0.0071,0.0057</t>
+  </si>
+  <si>
+    <t>0.6142,0.0057,0.0046,0.4825</t>
+  </si>
+  <si>
+    <t>0.9544,0.0223,0.0025,0.0062</t>
+  </si>
+  <si>
+    <t>0.0008,0.0747,0.9581,0.0704</t>
+  </si>
+  <si>
+    <t>0.9151,0.0100,0.0206,0.0154</t>
+  </si>
+  <si>
+    <t>0.8830,0.0047,0.0028,0.1007</t>
+  </si>
+  <si>
+    <t>0.4259,0.6447,0.0060,0.0028</t>
+  </si>
+  <si>
+    <t>0.7203,0.3264,0.0150,0.0088</t>
+  </si>
+  <si>
+    <t>0.9140,0.0645,0.0126,0.0069</t>
+  </si>
+  <si>
+    <t>0.0762,0.9081,0.0083,0.0016</t>
+  </si>
+  <si>
+    <t>0.7766,0.1411,0.1174,0.0184</t>
+  </si>
+  <si>
+    <t>0.8687,0.1257,0.0114,0.0043</t>
+  </si>
+  <si>
+    <t>0.9895,0.0020,0.0005,0.0020</t>
+  </si>
+  <si>
+    <t>0.9813,0.0028,0.0004,0.0055</t>
+  </si>
+  <si>
+    <t>0.9801,0.0074,0.0061,0.0016</t>
+  </si>
+  <si>
+    <t>0.9762,0.0035,0.0037,0.0070</t>
+  </si>
+  <si>
+    <t>0.9584,0.0541,0.0023,0.0007</t>
+  </si>
+  <si>
+    <t>0.9789,0.0176,0.0033,0.0008</t>
+  </si>
+  <si>
+    <t>0.9872,0.0151,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.9879,0.0047,0.0014,0.0010</t>
+  </si>
+  <si>
+    <t>0.3027,0.7333,0.0069,0.0141</t>
+  </si>
+  <si>
+    <t>0.4656,0.6417,0.0095,0.0031</t>
+  </si>
+  <si>
+    <t>0.7445,0.4458,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.6451,0.1263,0.3126,0.0114</t>
+  </si>
+  <si>
+    <t>0.9441,0.0994,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.8775,0.1151,0.0237,0.0065</t>
+  </si>
+  <si>
+    <t>0.9050,0.1650,0.0061,0.0005</t>
+  </si>
+  <si>
+    <t>0.8373,0.2517,0.0044,0.0025</t>
+  </si>
+  <si>
+    <t>0.0062,0.0418,0.9898,0.0003</t>
+  </si>
+  <si>
+    <t>0.8242,0.3128,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.0131,0.0115,0.9859,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.2240,0.9793,0.0037</t>
+  </si>
+  <si>
+    <t>0.0902,0.0275,0.9024,0.0039</t>
+  </si>
+  <si>
+    <t>0.0049,0.4130,0.9713,0.0014</t>
+  </si>
+  <si>
+    <t>0.0074,0.0155,0.9797,0.0048</t>
+  </si>
+  <si>
+    <t>0.0089,0.0019,0.9904,0.0005</t>
+  </si>
+  <si>
+    <t>0.0021,0.0175,0.9841,0.0057</t>
+  </si>
+  <si>
+    <t>0.2916,0.0388,0.7289,0.0053</t>
+  </si>
+  <si>
+    <t>0.2695,0.0665,0.7311,0.0050</t>
+  </si>
+  <si>
+    <t>0.1232,0.0218,0.8900,0.0011</t>
+  </si>
+  <si>
+    <t>0.6273,0.0290,0.4203,0.0002</t>
+  </si>
+  <si>
+    <t>0.0120,0.9273,0.1210,0.0008</t>
+  </si>
+  <si>
+    <t>0.2065,0.6062,0.1612,0.0041</t>
+  </si>
+  <si>
+    <t>0.0566,0.8204,0.1230,0.0498</t>
+  </si>
+  <si>
+    <t>0.5898,0.0930,0.3290,0.0221</t>
+  </si>
+  <si>
+    <t>0.8393,0.2846,0.0034,0.0006</t>
+  </si>
+  <si>
+    <t>0.8836,0.1986,0.0033,0.0017</t>
+  </si>
+  <si>
+    <t>0.8882,0.1546,0.0111,0.0024</t>
+  </si>
+  <si>
+    <t>0.9271,0.1407,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.8224,0.3187,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.6404,0.1665,0.1551,0.0037</t>
+  </si>
+  <si>
+    <t>0.8410,0.0210,0.1227,0.0074</t>
+  </si>
+  <si>
+    <t>0.6657,0.0659,0.2279,0.0306</t>
+  </si>
+  <si>
+    <t>0.6827,0.0415,0.2794,0.0201</t>
+  </si>
+  <si>
+    <t>0.5962,0.0371,0.4655,0.0033</t>
+  </si>
+  <si>
+    <t>0.4624,0.1319,0.3849,0.0868</t>
+  </si>
+  <si>
+    <t>0.1036,0.3225,0.6960,0.0482</t>
+  </si>
+  <si>
+    <t>0.1220,0.1691,0.7651,0.0084</t>
+  </si>
+  <si>
+    <t>0.0588,0.0454,0.9112,0.0217</t>
+  </si>
+  <si>
+    <t>0.0072,0.2359,0.9396,0.0094</t>
+  </si>
+  <si>
+    <t>0.9771,0.0102,0.0007,0.0029</t>
+  </si>
+  <si>
+    <t>0.9819,0.0240,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9621,0.0641,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.9734,0.0524,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9775,0.0160,0.0075,0.0015</t>
+  </si>
+  <si>
+    <t>0.9915,0.0025,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9914,0.0027,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.9605,0.0509,0.0025,0.0008</t>
+  </si>
+  <si>
+    <t>0.0144,0.0355,0.9688,0.0052</t>
+  </si>
+  <si>
+    <t>0.3144,0.1117,0.7060,0.0055</t>
+  </si>
+  <si>
+    <t>0.5964,0.1033,0.3511,0.0047</t>
+  </si>
+  <si>
+    <t>0.0179,0.0689,0.9628,0.0026</t>
+  </si>
+  <si>
+    <t>0.0017,0.0720,0.9908,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.0528,0.9917,0.0003</t>
+  </si>
+  <si>
+    <t>0.0006,0.0350,0.9932,0.0009</t>
+  </si>
+  <si>
+    <t>0.0390,0.2626,0.7815,0.0122</t>
+  </si>
+  <si>
+    <t>0.0174,0.0065,0.9862,0.0005</t>
+  </si>
+  <si>
+    <t>0.0143,0.0417,0.8480,0.1196</t>
+  </si>
+  <si>
+    <t>0.1866,0.5595,0.3272,0.0769</t>
+  </si>
+  <si>
+    <t>0.5777,0.0156,0.4403,0.0362</t>
+  </si>
+  <si>
+    <t>0.7116,0.0280,0.2609,0.0422</t>
+  </si>
+  <si>
+    <t>0.6298,0.0270,0.4177,0.0119</t>
+  </si>
+  <si>
+    <t>0.9447,0.0779,0.0076,0.0010</t>
+  </si>
+  <si>
+    <t>0.9913,0.0029,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.9930,0.0057,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9886,0.0077,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.8854,0.1802,0.0079,0.0023</t>
+  </si>
+  <si>
+    <t>0.9847,0.0172,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9942,0.0019,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9729,0.0462,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0106,0.0368,0.9676,0.0031</t>
+  </si>
+  <si>
+    <t>0.0016,0.4027,0.9752,0.0006</t>
+  </si>
+  <si>
+    <t>0.0069,0.0165,0.9866,0.0012</t>
+  </si>
+  <si>
+    <t>0.0676,0.2591,0.5374,0.0027</t>
+  </si>
+  <si>
+    <t>0.0042,0.0048,0.9747,0.0290</t>
+  </si>
+  <si>
+    <t>0.2261,0.0897,0.2162,0.5890</t>
+  </si>
+  <si>
+    <t>0.2241,0.1062,0.7241,0.0289</t>
+  </si>
+  <si>
+    <t>0.0466,0.0385,0.5782,0.4903</t>
+  </si>
+  <si>
+    <t>0.6341,0.0009,0.0116,0.3698</t>
+  </si>
+  <si>
+    <t>0.0432,0.1641,0.0348,0.9407</t>
+  </si>
+  <si>
+    <t>0.0085,0.0040,0.0004,0.9955</t>
+  </si>
+  <si>
+    <t>0.0046,0.0005,0.0007,0.9976</t>
+  </si>
+  <si>
+    <t>0.0014,0.0020,0.0025,0.9978</t>
+  </si>
+  <si>
+    <t>0.7800,0.0251,0.0040,0.1559</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,10 +2175,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,10 +2245,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,10 +2315,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2413,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2651,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,10 +2945,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +3001,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3869,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3939,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4009,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,10 +4849,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,10 +5171,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
